--- a/docentes/Velasco Sánchez David - Estadisticos 20232.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -85,55 +85,43 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
-    <t>AMECA</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
   </si>
   <si>
     <t>ESPINDOLA</t>
   </si>
   <si>
-    <t>EZEQUIEL</t>
-  </si>
-  <si>
     <t>JOSUE EDUARDO</t>
   </si>
   <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>DARINKA</t>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
   </si>
   <si>
     <t>ROSA ITZEL</t>
@@ -732,16 +720,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -755,16 +746,19 @@
         <v>37</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>37</v>
       </c>
-      <c r="E3">
-        <v>37</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -778,16 +772,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H4">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -801,16 +798,19 @@
         <v>31</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>31</v>
       </c>
-      <c r="E5">
-        <v>31</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -824,16 +824,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H6">
+        <v>6.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -847,16 +850,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>91.89</v>
+      </c>
+      <c r="H7">
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -912,16 +918,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>90</v>
+        <v>83.33</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -938,16 +944,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -973,7 +979,7 @@
         <v>91.67</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -999,7 +1005,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1016,16 +1022,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>67.86</v>
+        <v>75</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1051,7 +1057,7 @@
         <v>91.89</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -1061,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1093,22 +1099,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920287</v>
+        <v>21330051920334</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1116,22 +1122,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920334</v>
+        <v>21330051920386</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1139,94 +1145,71 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920088</v>
+        <v>20330051920235</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920192</v>
+        <v>21330051920307</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920214</v>
+        <v>21330051920330</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920330</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Velasco Sánchez David - Estadisticos 20232.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,48 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>ROSA ITZEL</t>
   </si>
 </sst>
 </file>
@@ -600,7 +558,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -609,7 +567,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -795,7 +753,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -804,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -918,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -970,13 +928,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H4">
         <v>8.4</v>
@@ -990,7 +948,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -999,7 +957,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -1022,16 +980,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1048,16 +1006,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>91.89</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1097,121 +1055,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920334</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920386</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920235</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920307</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920330</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
